--- a/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WPP_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="92">
   <si>
     <t>WPP</t>
   </si>
@@ -656,517 +656,543 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4227800</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4207700</v>
+      </c>
+      <c r="F8" s="3">
         <v>4634600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>4628700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>4564300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>4304300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>4703500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>5035500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>4566700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>4563800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>4855600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>4651800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>4588200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>4466700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>4622800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>4572000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8613700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>8503100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>4106100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>7609200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>3454700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>7656000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>3512000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>6810300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>3811700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>9363600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>5576900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>8744700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>4927000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>7335700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>4628400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>9686600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4595900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>10635100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>4759400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>9978500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>4831200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>10340000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>4754900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3693800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>3676200</v>
+      </c>
+      <c r="F9" s="3">
         <v>3753700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>3749000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>3991000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>3763600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>3820200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>4089900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>3909500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>3907000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>3928900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>3764100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>3912100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>3808500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3724300</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T9" s="3">
         <v>7278400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6887300</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W9" s="3">
         <v>6447300</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3">
         <v>6181000</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA9" s="3">
         <v>5861300</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC9" s="3">
         <v>7495800</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE9" s="3">
         <v>7317500</v>
       </c>
-      <c r="AD9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3">
         <v>5732800</v>
       </c>
-      <c r="AF9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI9" s="3">
         <v>8039600</v>
       </c>
-      <c r="AH9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK9" s="3">
         <v>8278100</v>
       </c>
-      <c r="AJ9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM9" s="3">
         <v>8194100</v>
       </c>
-      <c r="AL9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO9" s="3">
         <v>13701700</v>
       </c>
-      <c r="AN9" s="3" t="s">
+      <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>531500</v>
+      </c>
+      <c r="F10" s="3">
         <v>880900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>879800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>573400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>540700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>883200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>945600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>657200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>656700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>926700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>887800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>676100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>658200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>898500</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T10" s="3">
         <v>1335300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1615800</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W10" s="3">
         <v>1161900</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3">
         <v>1475000</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA10" s="3">
         <v>949100</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC10" s="3">
         <v>1867800</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE10" s="3">
         <v>1427300</v>
       </c>
-      <c r="AD10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG10" s="3">
         <v>1602900</v>
       </c>
-      <c r="AF10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI10" s="3">
         <v>1647000</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK10" s="3">
         <v>2357000</v>
       </c>
-      <c r="AJ10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM10" s="3">
         <v>1784400</v>
       </c>
-      <c r="AL10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO10" s="3">
         <v>-3361800</v>
       </c>
-      <c r="AN10" s="3" t="s">
+      <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1207,8 +1233,10 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1323,8 +1351,14 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1439,172 +1473,184 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
         <v>-12100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>-12100</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3">
         <v>17500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>18800</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N14" s="3">
         <v>-27400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-26200</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>-24900</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>97000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>94400</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W14" s="3">
         <v>-14500</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>112900</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA14" s="3">
         <v>62700</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC14" s="3">
         <v>46600</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE14" s="3">
         <v>18700</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG14" s="3">
         <v>17300</v>
       </c>
-      <c r="AF14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI14" s="3">
         <v>36700</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI14" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AK14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM14" s="3">
         <v>25300</v>
       </c>
-      <c r="AL14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO14" s="3">
         <v>-295800</v>
       </c>
-      <c r="AN14" s="3" t="s">
+      <c r="AP14" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>77000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>76600</v>
+      </c>
+      <c r="F15" s="3">
         <v>34300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>34300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>91800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>86600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>80700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>86400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>83400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>83400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>89800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>86000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>80700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>78600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>75000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1641,11 +1687,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AF15" s="3" t="s">
-        <v>5</v>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>5</v>
@@ -1659,20 +1705,26 @@
       <c r="AJ15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AK15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AL15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM15" s="3">
         <v>127600</v>
       </c>
-      <c r="AL15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO15" s="3">
         <v>119600</v>
       </c>
-      <c r="AN15" s="3" t="s">
+      <c r="AP15" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1710,240 +1762,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4054700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>4035400</v>
+      </c>
+      <c r="F17" s="3">
         <v>4532300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>4526600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>4412900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>4161600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>4145100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>4437700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>4299400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>4296600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>4718600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>4520700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>4393800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>4277400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>4132700</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T17" s="3">
         <v>8023800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>7647000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W17" s="3">
         <v>6994600</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3">
         <v>7559900</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA17" s="3">
         <v>10228500</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC17" s="3">
         <v>8456200</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE17" s="3">
         <v>7944600</v>
       </c>
-      <c r="AD17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG17" s="3">
         <v>6829900</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI17" s="3">
         <v>8634900</v>
       </c>
-      <c r="AH17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK17" s="3">
         <v>9091000</v>
       </c>
-      <c r="AJ17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM17" s="3">
         <v>9033700</v>
       </c>
-      <c r="AL17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO17" s="3">
         <v>8352300</v>
       </c>
-      <c r="AN17" s="3" t="s">
+      <c r="AP17" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>173100</v>
+      </c>
+      <c r="E18" s="3">
+        <v>172300</v>
+      </c>
+      <c r="F18" s="3">
         <v>102300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>102200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>151400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>142800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>558400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>597800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>267300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>267100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>136900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>131200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>194400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>189300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>490200</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T18" s="3">
         <v>589900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>856100</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W18" s="3">
         <v>614600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3">
         <v>96100</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA18" s="3">
         <v>-3418200</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC18" s="3">
         <v>907500</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE18" s="3">
         <v>800200</v>
       </c>
-      <c r="AD18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG18" s="3">
         <v>505700</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI18" s="3">
         <v>1051700</v>
       </c>
-      <c r="AH18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK18" s="3">
         <v>1544000</v>
       </c>
-      <c r="AJ18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM18" s="3">
         <v>944800</v>
       </c>
-      <c r="AL18" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO18" s="3">
         <v>1987700</v>
       </c>
-      <c r="AN18" s="3" t="s">
+      <c r="AP18" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1984,588 +2050,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>13300</v>
+      </c>
+      <c r="E20" s="3">
+        <v>13200</v>
+      </c>
+      <c r="F20" s="3">
         <v>-8100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-8100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>16300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>17400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-32200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-32200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-13400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-12800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-16500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-16100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T20" s="3">
         <v>128700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>21900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W20" s="3">
         <v>57400</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-164900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-265800</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC20" s="3">
         <v>429700</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE20" s="3">
         <v>3800</v>
       </c>
-      <c r="AD20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG20" s="3">
         <v>224700</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI20" s="3">
         <v>210900</v>
       </c>
-      <c r="AH20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK20" s="3">
         <v>361800</v>
       </c>
-      <c r="AJ20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM20" s="3">
         <v>239100</v>
       </c>
-      <c r="AL20" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO20" s="3">
         <v>109800</v>
       </c>
-      <c r="AN20" s="3" t="s">
+      <c r="AP20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>236800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>235700</v>
+      </c>
+      <c r="F21" s="3">
         <v>144700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>144500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>247300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>233200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>622800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>666800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>382900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>382700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>240100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>230000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>291600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>283900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>568100</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T21" s="3">
         <v>352700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1568900</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3">
         <v>683700</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC21" s="3">
         <v>1782500</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE21" s="3">
         <v>1298100</v>
       </c>
-      <c r="AD21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG21" s="3">
         <v>1169300</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI21" s="3">
         <v>1536000</v>
       </c>
-      <c r="AH21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK21" s="3">
         <v>2206400</v>
       </c>
-      <c r="AJ21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM21" s="3">
         <v>1486100</v>
       </c>
-      <c r="AL21" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO21" s="3">
         <v>2400000</v>
       </c>
-      <c r="AN21" s="3" t="s">
+      <c r="AP21" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>115400</v>
+      </c>
+      <c r="E22" s="3">
+        <v>114900</v>
+      </c>
+      <c r="F22" s="3">
         <v>111000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>110900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>121900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>115000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>123300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>132000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>132700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>132600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>94300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>90300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>146800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>142900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>125700</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>184800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>168600</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W22" s="3">
         <v>182600</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3">
         <v>180700</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA22" s="3">
         <v>191900</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC22" s="3">
         <v>238900</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE22" s="3">
         <v>242400</v>
       </c>
-      <c r="AD22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG22" s="3">
         <v>187400</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI22" s="3">
         <v>168200</v>
       </c>
-      <c r="AH22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK22" s="3">
         <v>171000</v>
       </c>
-      <c r="AJ22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM22" s="3">
         <v>167600</v>
       </c>
-      <c r="AL22" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO22" s="3">
         <v>167900</v>
       </c>
-      <c r="AN22" s="3" t="s">
+      <c r="AP22" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>70300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>70000</v>
+      </c>
+      <c r="F23" s="3">
         <v>22200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>22200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>67100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>63300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>433800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>464400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>213600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>213400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>90400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>86600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>129600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>126200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>446500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T23" s="3">
         <v>533800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>709500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W23" s="3">
         <v>489400</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-249500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="3">
         <v>-3875900</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC23" s="3">
         <v>1098300</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE23" s="3">
         <v>561600</v>
       </c>
-      <c r="AD23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG23" s="3">
         <v>543000</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI23" s="3">
         <v>1094400</v>
       </c>
-      <c r="AH23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK23" s="3">
         <v>1734900</v>
       </c>
-      <c r="AJ23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM23" s="3">
         <v>1016300</v>
       </c>
-      <c r="AL23" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO23" s="3">
         <v>1929600</v>
       </c>
-      <c r="AN23" s="3" t="s">
+      <c r="AP23" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>45800</v>
+      </c>
+      <c r="E24" s="3">
+        <v>45600</v>
+      </c>
+      <c r="F24" s="3">
         <v>185100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>184800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>19200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>18100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>194000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>207700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>58100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>58100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>59900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>57400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>34900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>34000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>160800</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T24" s="3">
         <v>149800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>156800</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W24" s="3">
         <v>132900</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y24" s="3">
         <v>125600</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="3">
         <v>13300</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC24" s="3">
         <v>226000</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE24" s="3">
         <v>150100</v>
       </c>
-      <c r="AD24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG24" s="3">
         <v>151900</v>
       </c>
-      <c r="AF24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI24" s="3">
         <v>182300</v>
       </c>
-      <c r="AH24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK24" s="3">
         <v>335900</v>
       </c>
-      <c r="AJ24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM24" s="3">
         <v>189800</v>
       </c>
-      <c r="AL24" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO24" s="3">
         <v>323700</v>
       </c>
-      <c r="AN24" s="3" t="s">
+      <c r="AP24" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2680,240 +2778,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>24400</v>
+      </c>
+      <c r="F26" s="3">
         <v>-162900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-162600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>48000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>45200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>239700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>256700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>155400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>155300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>30600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>29300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>94700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>92200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>285700</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T26" s="3">
         <v>383900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>552600</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W26" s="3">
         <v>356500</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-375000</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-3889200</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC26" s="3">
         <v>872300</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE26" s="3">
         <v>411500</v>
       </c>
-      <c r="AD26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG26" s="3">
         <v>391100</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI26" s="3">
         <v>912100</v>
       </c>
-      <c r="AH26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK26" s="3">
         <v>1399000</v>
       </c>
-      <c r="AJ26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM26" s="3">
         <v>826500</v>
       </c>
-      <c r="AL26" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO26" s="3">
         <v>1606000</v>
       </c>
-      <c r="AN26" s="3" t="s">
+      <c r="AP26" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F27" s="3">
         <v>-174300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-174100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>30100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>28400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>210900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>225800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>129500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>129500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>-1300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-1200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>71200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>69300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>255900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T27" s="3">
         <v>328800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>490900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W27" s="3">
         <v>313600</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-414200</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA27" s="3">
         <v>-3914900</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC27" s="3">
         <v>805900</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE27" s="3">
         <v>369700</v>
       </c>
-      <c r="AD27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG27" s="3">
         <v>348800</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI27" s="3">
         <v>869300</v>
       </c>
-      <c r="AH27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK27" s="3">
         <v>1323200</v>
       </c>
-      <c r="AJ27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM27" s="3">
         <v>777500</v>
       </c>
-      <c r="AL27" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO27" s="3">
         <v>1520000</v>
       </c>
-      <c r="AN27" s="3" t="s">
+      <c r="AP27" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3028,8 +3144,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3072,14 +3194,14 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>5</v>
@@ -3091,50 +3213,50 @@
         <v>5</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y29" s="3">
         <v>15900</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-8300</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-64100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>59300</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>166900</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>268700</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3144,8 +3266,14 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3260,8 +3388,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3376,240 +3510,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="F32" s="3">
         <v>8100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>8100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-16300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-17400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>32200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>32200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>13400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>12800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>16500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>16100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>3000</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T32" s="3">
         <v>-128700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-21900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W32" s="3">
         <v>-57400</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y32" s="3">
         <v>164900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA32" s="3">
         <v>265800</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-429700</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE32" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG32" s="3">
         <v>-224700</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI32" s="3">
         <v>-210900</v>
       </c>
-      <c r="AH32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK32" s="3">
         <v>-361800</v>
       </c>
-      <c r="AJ32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM32" s="3">
         <v>-239100</v>
       </c>
-      <c r="AL32" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO32" s="3">
         <v>-109800</v>
       </c>
-      <c r="AN32" s="3" t="s">
+      <c r="AP32" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F33" s="3">
         <v>-174300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-174100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>30100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>28400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>210900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>225800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>129500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>129500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>-1300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>71200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>69300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>255900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T33" s="3">
         <v>328800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>490900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3">
         <v>313600</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-398300</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA33" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC33" s="3">
         <v>741800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE33" s="3">
         <v>429000</v>
       </c>
-      <c r="AD33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG33" s="3">
         <v>515800</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI33" s="3">
         <v>869300</v>
       </c>
-      <c r="AH33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK33" s="3">
         <v>1591900</v>
       </c>
-      <c r="AJ33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM33" s="3">
         <v>777500</v>
       </c>
-      <c r="AL33" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO33" s="3">
         <v>1520000</v>
       </c>
-      <c r="AN33" s="3" t="s">
+      <c r="AP33" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3724,245 +3876,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F35" s="3">
         <v>-174300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-174100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>30100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>28400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>210900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>225800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>129500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>129500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>-1300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>71200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>69300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>255900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T35" s="3">
         <v>328800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>490900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W35" s="3">
         <v>313600</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-398300</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA35" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC35" s="3">
         <v>741800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE35" s="3">
         <v>429000</v>
       </c>
-      <c r="AD35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG35" s="3">
         <v>515800</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI35" s="3">
         <v>869300</v>
       </c>
-      <c r="AH35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK35" s="3">
         <v>1591900</v>
       </c>
-      <c r="AJ35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM35" s="3">
         <v>777500</v>
       </c>
-      <c r="AL35" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO35" s="3">
         <v>1520000</v>
       </c>
-      <c r="AN35" s="3" t="s">
+      <c r="AP35" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4003,8 +4173,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4045,124 +4217,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3135200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3120300</v>
+      </c>
+      <c r="F41" s="3">
         <v>3625800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>3621300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1968800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1856600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>3302600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>3535700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2689300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2687600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>2825200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>2706700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2494100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>2428000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2737000</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T41" s="3">
         <v>16447600</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V41" s="3">
+      <c r="V41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X41" s="3">
         <v>13482200</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AA41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC41" s="3">
         <v>15418600</v>
       </c>
-      <c r="AB41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE41" s="3">
         <v>2984200</v>
       </c>
-      <c r="AD41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG41" s="3">
         <v>3491100</v>
       </c>
-      <c r="AF41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI41" s="3">
         <v>2871300</v>
       </c>
-      <c r="AH41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK41" s="3">
         <v>3119100</v>
       </c>
-      <c r="AJ41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM41" s="3">
         <v>3725100</v>
       </c>
-      <c r="AL41" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO41" s="3">
         <v>2970900</v>
       </c>
-      <c r="AN41" s="3" t="s">
+      <c r="AP41" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4203,14 +4383,14 @@
         <v>0</v>
       </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>265000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -4259,11 +4439,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-      <c r="AI42" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AJ42" s="3" t="s">
-        <v>5</v>
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
       </c>
       <c r="AK42" s="3" t="s">
         <v>5</v>
@@ -4271,130 +4451,142 @@
       <c r="AL42" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AM42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AN42" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO42" s="3">
         <v>237900</v>
       </c>
-      <c r="AN42" s="3" t="s">
+      <c r="AP42" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>13676500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>13611400</v>
+      </c>
+      <c r="F43" s="3">
         <v>13819700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>13802200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>14267700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>13455000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>13522000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>14476600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>14213900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>14204700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>14630400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>14016500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>13801800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>13436300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>14898600</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T43" s="3">
         <v>13478100</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V43" s="3">
+      <c r="V43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X43" s="3">
         <v>27605700</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X43" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AA43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC43" s="3">
         <v>15478600</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE43" s="3">
         <v>17299200</v>
       </c>
-      <c r="AD43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG43" s="3">
         <v>16701500</v>
       </c>
-      <c r="AF43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI43" s="3">
         <v>15659500</v>
       </c>
-      <c r="AH43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK43" s="3">
         <v>15736500</v>
       </c>
-      <c r="AJ43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM43" s="3">
         <v>14605800</v>
       </c>
-      <c r="AL43" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO43" s="3">
         <v>16171500</v>
       </c>
-      <c r="AN43" s="3" t="s">
+      <c r="AP43" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4440,657 +4632,693 @@
       <c r="Q44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R44" s="3">
+      <c r="R44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T44" s="3">
         <v>336800</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V44" s="3">
+      <c r="V44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X44" s="3">
         <v>416800</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X44" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AA44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC44" s="3">
         <v>476600</v>
       </c>
-      <c r="AB44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE44" s="3">
         <v>576100</v>
       </c>
-      <c r="AD44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG44" s="3">
         <v>484100</v>
       </c>
-      <c r="AF44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI44" s="3">
         <v>524600</v>
       </c>
-      <c r="AH44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK44" s="3">
         <v>1076600</v>
       </c>
-      <c r="AJ44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM44" s="3">
         <v>1113600</v>
       </c>
-      <c r="AL44" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO44" s="3">
         <v>527200</v>
       </c>
-      <c r="AN44" s="3" t="s">
+      <c r="AP44" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3">
         <v>4000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4000</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>1300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>3000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>6100</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T45" s="3">
         <v>316600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V45" s="3">
+      <c r="V45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X45" s="3">
         <v>922800</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AA45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC45" s="3">
         <v>1055300</v>
       </c>
-      <c r="AB45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE45" s="3">
         <v>550600</v>
       </c>
-      <c r="AD45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="3">
         <v>381200</v>
       </c>
-      <c r="AF45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI45" s="3">
         <v>546200</v>
       </c>
-      <c r="AH45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK45" s="3">
         <v>390400</v>
       </c>
-      <c r="AJ45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM45" s="3">
         <v>529400</v>
       </c>
-      <c r="AL45" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO45" s="3">
         <v>427600</v>
       </c>
-      <c r="AN45" s="3" t="s">
+      <c r="AP45" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>16811700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>16731700</v>
+      </c>
+      <c r="F46" s="3">
         <v>17725400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>17703000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>16236500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>15311600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17102500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18309900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16903200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16892300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>17761200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>17016100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>16687400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>16245400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>18191800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T46" s="3">
         <v>30579100</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V46" s="3">
+      <c r="V46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X46" s="3">
         <v>28329100</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AA46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC46" s="3">
         <v>32429200</v>
       </c>
-      <c r="AB46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE46" s="3">
         <v>21410100</v>
       </c>
-      <c r="AD46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG46" s="3">
         <v>21057900</v>
       </c>
-      <c r="AF46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI46" s="3">
         <v>19601700</v>
       </c>
-      <c r="AH46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK46" s="3">
         <v>19769200</v>
       </c>
-      <c r="AJ46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM46" s="3">
         <v>19395900</v>
       </c>
-      <c r="AL46" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO46" s="3">
         <v>20335200</v>
       </c>
-      <c r="AN46" s="3" t="s">
+      <c r="AP46" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>696600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>693200</v>
+      </c>
+      <c r="F47" s="3">
         <v>760400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>759500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>800100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>754500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>815000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>872500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>711500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>711100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>789700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>756600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>738300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>718800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>813200</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T47" s="3">
         <v>947100</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V47" s="3">
+      <c r="V47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X47" s="3">
         <v>1727800</v>
       </c>
-      <c r="W47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AA47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC47" s="3">
         <v>1788300</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE47" s="3">
         <v>1804800</v>
       </c>
-      <c r="AD47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG47" s="3">
         <v>1933000</v>
       </c>
-      <c r="AF47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI47" s="3">
         <v>2366400</v>
       </c>
-      <c r="AH47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK47" s="3">
         <v>2893900</v>
       </c>
-      <c r="AJ47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM47" s="3">
         <v>3138300</v>
       </c>
-      <c r="AL47" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO47" s="3">
         <v>3133600</v>
       </c>
-      <c r="AN47" s="3" t="s">
+      <c r="AP47" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2579300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="F48" s="3">
         <v>2747000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>2743500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>3064800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>2890200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>2871900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>3074700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>2713400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>2711600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2815000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>2696900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>3046000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>2965300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3047400</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T48" s="3">
         <v>2926900</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V48" s="3">
+      <c r="V48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X48" s="3">
         <v>3113000</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X48" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AA48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC48" s="3">
         <v>3560200</v>
       </c>
-      <c r="AB48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE48" s="3">
         <v>3858100</v>
       </c>
-      <c r="AD48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG48" s="3">
         <v>1430400</v>
       </c>
-      <c r="AF48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI48" s="3">
         <v>1332600</v>
       </c>
-      <c r="AH48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK48" s="3">
         <v>1277600</v>
       </c>
-      <c r="AJ48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM48" s="3">
         <v>1213700</v>
       </c>
-      <c r="AL48" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO48" s="3">
         <v>1275600</v>
       </c>
-      <c r="AN48" s="3" t="s">
+      <c r="AP48" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10335700</v>
+      </c>
+      <c r="E49" s="3">
+        <v>10286500</v>
+      </c>
+      <c r="F49" s="3">
         <v>10336500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>10323400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>11061800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>10431700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>10449800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>11187500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>11548500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>11541100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>11768200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>11274500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>12450900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>12121100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>11934800</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T49" s="3">
         <v>11193000</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V49" s="3">
+      <c r="V49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X49" s="3">
         <v>13808600</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X49" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AA49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC49" s="3">
         <v>15791900</v>
       </c>
-      <c r="AB49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE49" s="3">
         <v>20650400</v>
       </c>
-      <c r="AD49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG49" s="3">
         <v>19871000</v>
       </c>
-      <c r="AF49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI49" s="3">
         <v>19246300</v>
       </c>
-      <c r="AH49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK49" s="3">
         <v>19527200</v>
       </c>
-      <c r="AJ49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM49" s="3">
         <v>19816900</v>
       </c>
-      <c r="AL49" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO49" s="3">
         <v>20320200</v>
       </c>
-      <c r="AN49" s="3" t="s">
+      <c r="AP49" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5205,8 +5433,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5321,124 +5555,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>452400</v>
+      </c>
+      <c r="E52" s="3">
+        <v>450300</v>
+      </c>
+      <c r="F52" s="3">
         <v>440100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>439600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>471300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>444500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>291700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>312300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>315900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>315700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>364300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>349000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>329400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>320700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>352700</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T52" s="3">
         <v>470600</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V52" s="3">
+      <c r="V52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X52" s="3">
         <v>388200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X52" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z52" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AA52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC52" s="3">
         <v>443900</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE52" s="3">
         <v>464300</v>
       </c>
-      <c r="AD52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG52" s="3">
         <v>439800</v>
       </c>
-      <c r="AF52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI52" s="3">
         <v>439900</v>
       </c>
-      <c r="AH52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK52" s="3">
         <v>438900</v>
       </c>
-      <c r="AJ52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM52" s="3">
         <v>466900</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO52" s="3">
         <v>454700</v>
       </c>
-      <c r="AN52" s="3" t="s">
+      <c r="AP52" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5553,124 +5799,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>31279000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>31130100</v>
+      </c>
+      <c r="F54" s="3">
         <v>32402400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>32361500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>32051000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>30225200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>31935400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>34189800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>32622200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>32601200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>33911200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>32488500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>33617700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>32727300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>34728000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T54" s="3">
         <v>46116700</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V54" s="3">
+      <c r="V54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X54" s="3">
         <v>47202600</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z54" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AA54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC54" s="3">
         <v>54013400</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE54" s="3">
         <v>48187700</v>
       </c>
-      <c r="AD54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG54" s="3">
         <v>44732100</v>
       </c>
-      <c r="AF54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI54" s="3">
         <v>42987000</v>
       </c>
-      <c r="AH54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK54" s="3">
         <v>43906700</v>
       </c>
-      <c r="AJ54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM54" s="3">
         <v>44031700</v>
       </c>
-      <c r="AL54" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO54" s="3">
         <v>45519200</v>
       </c>
-      <c r="AN54" s="3" t="s">
+      <c r="AP54" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5711,8 +5969,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5753,538 +6013,564 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16691000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>16611500</v>
+      </c>
+      <c r="F57" s="3">
         <v>13549100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>13532000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>15162400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>14298600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>13316700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>14256800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>15054300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>15044600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>13789700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>13211100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>11883300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>11568600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>13473500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T57" s="3">
         <v>13088000</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V57" s="3">
+      <c r="V57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X57" s="3">
         <v>29450100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X57" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AA57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC57" s="3">
         <v>14330400</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE57" s="3">
         <v>13887500</v>
       </c>
-      <c r="AD57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG57" s="3">
         <v>14096100</v>
       </c>
-      <c r="AF57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI57" s="3">
         <v>12676500</v>
       </c>
-      <c r="AH57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK57" s="3">
         <v>13139200</v>
       </c>
-      <c r="AJ57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM57" s="3">
         <v>12223200</v>
       </c>
-      <c r="AL57" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO57" s="3">
         <v>13939300</v>
       </c>
-      <c r="AN57" s="3" t="s">
+      <c r="AP57" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2264800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>2254000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1406500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1404700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1586500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1496100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1031600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1104400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1850200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1849000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1576900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1510800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1767800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1721000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1748800</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T58" s="3">
         <v>11403200</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V58" s="3">
+      <c r="V58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X58" s="3">
         <v>21343800</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X58" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AA58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC58" s="3">
         <v>12732200</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE58" s="3">
         <v>2091600</v>
       </c>
-      <c r="AD58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG58" s="3">
         <v>1353900</v>
       </c>
-      <c r="AF58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI58" s="3">
         <v>413100</v>
       </c>
-      <c r="AH58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK58" s="3">
         <v>1628000</v>
       </c>
-      <c r="AJ58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM58" s="3">
         <v>2433800</v>
       </c>
-      <c r="AL58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO58" s="3">
         <v>1320100</v>
       </c>
-      <c r="AN58" s="3" t="s">
+      <c r="AP58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>465700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>463500</v>
+      </c>
+      <c r="F59" s="3">
         <v>5010800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>5004400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>2103000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1983200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5076600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5434900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>2037200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>2035900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>5402000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>5175400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5246900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>5107900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>6114300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T59" s="3">
         <v>5125600</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V59" s="3">
+      <c r="V59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X59" s="3">
         <v>5603100</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z59" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AA59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC59" s="3">
         <v>6277400</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE59" s="3">
         <v>6517600</v>
       </c>
-      <c r="AD59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG59" s="3">
         <v>6487500</v>
       </c>
-      <c r="AF59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI59" s="3">
         <v>6098600</v>
       </c>
-      <c r="AH59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK59" s="3">
         <v>6282500</v>
       </c>
-      <c r="AJ59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM59" s="3">
         <v>6122800</v>
       </c>
-      <c r="AL59" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO59" s="3">
         <v>6816900</v>
       </c>
-      <c r="AN59" s="3" t="s">
+      <c r="AP59" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19421500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>19329100</v>
+      </c>
+      <c r="F60" s="3">
         <v>19966400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>19941100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>18851900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>17778000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>19424900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>20796100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>18941700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>18929500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>20768600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>19897200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>18898000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>18397400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>21336600</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T60" s="3">
         <v>29616900</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V60" s="3">
+      <c r="V60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X60" s="3">
         <v>28685000</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X60" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AA60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC60" s="3">
         <v>32674500</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE60" s="3">
         <v>22496700</v>
       </c>
-      <c r="AD60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG60" s="3">
         <v>21937500</v>
       </c>
-      <c r="AF60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI60" s="3">
         <v>19188100</v>
       </c>
-      <c r="AH60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK60" s="3">
         <v>20235700</v>
       </c>
-      <c r="AJ60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM60" s="3">
         <v>19563000</v>
       </c>
-      <c r="AL60" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO60" s="3">
         <v>22076200</v>
       </c>
-      <c r="AN60" s="3" t="s">
+      <c r="AP60" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>7264200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>7229600</v>
+      </c>
+      <c r="F61" s="3">
         <v>7788700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>7778900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>7666800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>7230100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>6915600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>7403800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>7681300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>7676400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>7180200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>6878900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>7934700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>7724500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>6904000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
         <v>8680900</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>7148900</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -6292,165 +6578,177 @@
         <v>0</v>
       </c>
       <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="3">
         <v>8175600</v>
       </c>
-      <c r="AB61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="3">
         <v>9978600</v>
       </c>
-      <c r="AD61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
         <v>7442400</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="3">
         <v>8446400</v>
       </c>
-      <c r="AH61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK61" s="3">
         <v>8152500</v>
       </c>
-      <c r="AJ61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM61" s="3">
         <v>8598700</v>
       </c>
-      <c r="AL61" s="3">
-        <v>0</v>
-      </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO61" s="3">
         <v>7327800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>529400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>526900</v>
+      </c>
+      <c r="F62" s="3">
         <v>547800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>547100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>449400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>423800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>577100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>617900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>595200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>594900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>678900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>650400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>1018200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>991200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>886200</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T62" s="3">
         <v>1379500</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V62" s="3">
+      <c r="V62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X62" s="3">
         <v>2010300</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X62" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AA62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC62" s="3">
         <v>1685900</v>
       </c>
-      <c r="AB62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE62" s="3">
         <v>1930800</v>
       </c>
-      <c r="AD62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG62" s="3">
         <v>2399700</v>
       </c>
-      <c r="AF62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI62" s="3">
         <v>2432700</v>
       </c>
-      <c r="AH62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK62" s="3">
         <v>2532700</v>
       </c>
-      <c r="AJ62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM62" s="3">
         <v>3021700</v>
       </c>
-      <c r="AL62" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO62" s="3">
         <v>3253300</v>
       </c>
-      <c r="AN62" s="3" t="s">
+      <c r="AP62" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6565,8 +6863,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6681,8 +6985,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6797,124 +7107,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>27579900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>27448700</v>
+      </c>
+      <c r="F66" s="3">
         <v>28671600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>28635400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>27381800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>25822000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>27260700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>29185100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>27620200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>27602400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>29028900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>27811000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>28451800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>27698200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>29715200</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T66" s="3">
         <v>40082900</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V66" s="3">
+      <c r="V66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X66" s="3">
         <v>37750900</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X66" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AA66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC66" s="3">
         <v>43042600</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE66" s="3">
         <v>34961600</v>
       </c>
-      <c r="AD66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG66" s="3">
         <v>32340200</v>
       </c>
-      <c r="AF66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI66" s="3">
         <v>30603800</v>
       </c>
-      <c r="AH66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK66" s="3">
         <v>31532300</v>
       </c>
-      <c r="AJ66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM66" s="3">
         <v>31753700</v>
       </c>
-      <c r="AL66" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO66" s="3">
         <v>33240800</v>
       </c>
-      <c r="AN66" s="3" t="s">
+      <c r="AP66" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6955,8 +7277,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7071,8 +7395,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7187,8 +7517,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7303,8 +7639,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7419,124 +7761,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2834000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2820500</v>
+      </c>
+      <c r="F72" s="3">
         <v>2212700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2209900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>3869000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>3648600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>3096000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>3314600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>4559800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>4556800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>4000900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3833000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>4898300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>4768500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>4530000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T72" s="3">
         <v>6567300</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V72" s="3">
+      <c r="V72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X72" s="3">
         <v>10018900</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC72" s="3">
         <v>11619500</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE72" s="3">
         <v>13918500</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG72" s="3">
         <v>13121900</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI72" s="3">
         <v>13135200</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK72" s="3">
         <v>12986500</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM72" s="3">
         <v>12828500</v>
       </c>
-      <c r="AL72" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO72" s="3">
         <v>12629500</v>
       </c>
-      <c r="AN72" s="3" t="s">
+      <c r="AP72" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7651,8 +8005,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7767,8 +8127,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7883,124 +8249,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3452300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>3435900</v>
+      </c>
+      <c r="F76" s="3">
         <v>3418600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>3414300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4334800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4087900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4350400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4657600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4419500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4416600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>4300200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4119800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>4622100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>4499700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4435000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T76" s="3">
         <v>6033800</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="V76" s="3">
+      <c r="V76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X76" s="3">
         <v>9451700</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>5</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AA76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC76" s="3">
         <v>10970900</v>
       </c>
-      <c r="AB76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE76" s="3">
         <v>13226200</v>
       </c>
-      <c r="AD76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG76" s="3">
         <v>12391900</v>
       </c>
-      <c r="AF76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI76" s="3">
         <v>12383200</v>
       </c>
-      <c r="AH76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK76" s="3">
         <v>12374400</v>
       </c>
-      <c r="AJ76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM76" s="3">
         <v>12278000</v>
       </c>
-      <c r="AL76" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO76" s="3">
         <v>12278400</v>
       </c>
-      <c r="AN76" s="3" t="s">
+      <c r="AP76" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8115,245 +8493,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>12500</v>
+      </c>
+      <c r="F81" s="3">
         <v>-174300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-174100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>30100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>28400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>210900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>225800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>129500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>129500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>-1300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>71200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>69300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>255900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T81" s="3">
         <v>328800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>490900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="W81" s="3">
         <v>313600</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-398300</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AA81" s="3">
         <v>-3923200</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC81" s="3">
         <v>741800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE81" s="3">
         <v>429000</v>
       </c>
-      <c r="AD81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG81" s="3">
         <v>515800</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI81" s="3">
         <v>869300</v>
       </c>
-      <c r="AH81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK81" s="3">
         <v>1591900</v>
       </c>
-      <c r="AJ81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM81" s="3">
         <v>777500</v>
       </c>
-      <c r="AL81" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO81" s="3">
         <v>1520000</v>
       </c>
-      <c r="AN81" s="3" t="s">
+      <c r="AP81" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8394,124 +8790,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E83" s="3">
+        <v>118200</v>
+      </c>
+      <c r="F83" s="3">
         <v>111400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>119300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>120700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>120600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>133100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>127500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>135300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>131800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>132000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>122200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>127500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>137900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>144600</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T83" s="3">
         <v>-357800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>665500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W83" s="3">
+      <c r="W83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y83" s="3">
         <v>710500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>0</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC83" s="3">
         <v>429900</v>
       </c>
-      <c r="AB83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE83" s="3">
         <v>468900</v>
       </c>
-      <c r="AD83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG83" s="3">
         <v>412000</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI83" s="3">
         <v>249800</v>
       </c>
-      <c r="AH83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK83" s="3">
         <v>277000</v>
       </c>
-      <c r="AJ83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM83" s="3">
         <v>278300</v>
       </c>
-      <c r="AL83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO83" s="3">
         <v>275200</v>
       </c>
-      <c r="AN83" s="3" t="s">
+      <c r="AP83" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8626,8 +9030,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8742,8 +9152,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8858,8 +9274,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8974,8 +9396,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9090,124 +9518,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-437800</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-435800</v>
+      </c>
+      <c r="F89" s="3">
         <v>1184400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1182900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-709700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-669300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1219400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1305500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-341200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-341000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>1071900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>1026900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-282800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-275300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>1104500</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T89" s="3">
         <v>-4008400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2592000</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W89" s="3">
+      <c r="W89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y89" s="3">
         <v>2450400</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>0</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC89" s="3">
         <v>2696100</v>
       </c>
-      <c r="AB89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE89" s="3">
         <v>-173600</v>
       </c>
-      <c r="AD89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG89" s="3">
         <v>2140900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI89" s="3">
         <v>94200</v>
       </c>
-      <c r="AH89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK89" s="3">
         <v>1724900</v>
       </c>
-      <c r="AJ89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM89" s="3">
         <v>111600</v>
       </c>
-      <c r="AL89" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO89" s="3">
         <v>2248600</v>
       </c>
-      <c r="AN89" s="3" t="s">
+      <c r="AP89" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9248,124 +9688,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-22400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-33000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-32900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-28800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-27100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-67000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-71700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-51800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-51800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-61100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-58600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-51500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-50100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-63900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-132200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-132200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-140500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-140500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-227100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-260300</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>0</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-263800</v>
       </c>
-      <c r="AB91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-200300</v>
       </c>
-      <c r="AD91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-207100</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-204300</v>
       </c>
-      <c r="AH91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-246400</v>
       </c>
-      <c r="AJ91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-130400</v>
       </c>
-      <c r="AL91" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO91" s="3">
         <v>-187600</v>
       </c>
-      <c r="AN91" s="3" t="s">
+      <c r="AP91" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9480,8 +9928,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9596,124 +10050,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-58100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-92900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-92700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-143200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-135000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>242900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>260000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-69500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-69500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-58600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-56100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-183000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-178100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-147400</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T94" s="3">
         <v>581700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-818900</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W94" s="3">
+      <c r="W94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-199900</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC94" s="3">
         <v>2316500</v>
       </c>
-      <c r="AB94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE94" s="3">
         <v>83800</v>
       </c>
-      <c r="AD94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-34200</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI94" s="3">
         <v>272000</v>
       </c>
-      <c r="AH94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-238300</v>
       </c>
-      <c r="AJ94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-413500</v>
       </c>
-      <c r="AL94" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO94" s="3">
         <v>-790700</v>
       </c>
-      <c r="AN94" s="3" t="s">
+      <c r="AP94" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9754,124 +10220,132 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
+      <c r="D96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F96" s="3">
         <v>230800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>230500</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H96" s="3">
+      <c r="H96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J96" s="3">
         <v>266000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>284800</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N96" s="3">
         <v>269400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>258100</v>
       </c>
-      <c r="N96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="O96" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="P96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R96" s="3">
         <v>220100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-401300</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-145500</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-1023500</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-987200</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-980200</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-811800</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9986,8 +10460,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10102,8 +10582,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10218,352 +10704,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>147300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>146600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-199200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-198900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-15800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-14900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-1115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-1194200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>501100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>500800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-780200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-747400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>204000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>198600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-643700</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T100" s="3">
         <v>1548600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2622900</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U100" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W100" s="3">
+      <c r="W100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-298700</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-3561900</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-426000</v>
       </c>
-      <c r="AD100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-1759300</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI100" s="3">
         <v>-364300</v>
       </c>
-      <c r="AH100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK100" s="3">
         <v>-1706200</v>
       </c>
-      <c r="AJ100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM100" s="3">
         <v>681500</v>
       </c>
-      <c r="AL100" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO100" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AN100" s="3" t="s">
+      <c r="AP100" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-21200</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-19400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-20800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-37300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-37300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-13400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-12800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-37500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-36500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-14600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-13300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>53500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>57800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T101" s="3">
         <v>278100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-165900</v>
       </c>
-      <c r="T101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U101" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V101" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W101" s="3">
+      <c r="W101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-118300</v>
       </c>
-      <c r="X101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>0</v>
-      </c>
       <c r="Z101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC101" s="3">
         <v>-138300</v>
       </c>
-      <c r="AB101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE101" s="3">
         <v>16100</v>
       </c>
-      <c r="AD101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG101" s="3">
         <v>21900</v>
       </c>
-      <c r="AF101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI101" s="3">
         <v>-101000</v>
       </c>
-      <c r="AH101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK101" s="3">
         <v>-58700</v>
       </c>
-      <c r="AJ101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM101" s="3">
         <v>23200</v>
       </c>
-      <c r="AL101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO101" s="3">
         <v>71900</v>
       </c>
-      <c r="AN101" s="3" t="s">
+      <c r="AP101" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-351600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-349900</v>
+      </c>
+      <c r="F102" s="3">
         <v>913900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>912700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-889800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-839200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>327400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>350500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>53100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>53000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>219700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>210500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-299300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-291300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>299100</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T102" s="3">
         <v>-1600000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-1015600</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W102" s="3">
+      <c r="W102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y102" s="3">
         <v>1833500</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y102" s="3">
-        <v>0</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC102" s="3">
         <v>1312400</v>
       </c>
-      <c r="AB102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE102" s="3">
         <v>-499700</v>
       </c>
-      <c r="AD102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG102" s="3">
         <v>369300</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AI102" s="3">
         <v>-99000</v>
       </c>
-      <c r="AH102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK102" s="3">
         <v>-278200</v>
       </c>
-      <c r="AJ102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AM102" s="3">
         <v>402900</v>
       </c>
-      <c r="AL102" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AO102" s="3">
         <v>397000</v>
       </c>
-      <c r="AN102" s="3" t="s">
+      <c r="AP102" s="3" t="s">
         <v>5</v>
       </c>
     </row>
